--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5483-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5483-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{463B635F-4FD5-49DC-8244-C30F7C5F4D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70AEE511-9878-4341-94F4-33C2E7279D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{9A4D88D8-1BE3-440F-A4C2-422BF40D40A8}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C45C4BBC-6E01-4120-BAA4-4E124DF217B8}"/>
   </bookViews>
   <sheets>
     <sheet name="5483-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1579,28 +1579,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9DF358D-BAF7-4A8C-8F2D-78A434329E7C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AF5D2BF-7501-4BA6-9F1B-E89A71A7B444}">
   <dimension ref="A1:X46"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1634,7 +1634,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1670,7 +1670,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1790,7 +1790,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40"/>
       <c r="B6" s="41"/>
       <c r="C6" s="43"/>
@@ -1898,7 +1898,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="48">
         <v>2024</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>7.64</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>30</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>4.1100000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>30</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="50">
         <v>2023</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>30</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>30</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="48">
         <v>2022</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>30</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>30</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="50">
         <v>2021</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>30</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>30</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="48">
         <v>2020</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>30</v>
       </c>
@@ -2998,7 +2998,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
         <v>30</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="50">
         <v>2019</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="48">
         <v>2018</v>
       </c>
@@ -3216,7 +3216,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="50">
         <v>2017</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>6.37</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="48">
         <v>2016</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>4.53</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="50">
         <v>2015</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>5.47</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="48">
         <v>2014</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="50">
         <v>2013</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="48">
         <v>2012</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="50">
         <v>2011</v>
       </c>
@@ -3720,7 +3720,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="48">
         <v>2010</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="50">
         <v>2009</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="48">
         <v>2008</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>7.73</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="50">
         <v>2007</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="48">
         <v>2006</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="50">
         <v>2005</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="48">
         <v>2004</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="50">
         <v>2003</v>
       </c>
@@ -4296,7 +4296,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="48">
         <v>2002</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="50">
         <v>2001</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="48">
         <v>2000</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="50">
         <v>1999</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="48">
         <v>1998</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="50">
         <v>1997</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="48" t="s">
         <v>65</v>
       </c>
